--- a/Data/Excel/wave.xlsx
+++ b/Data/Excel/wave.xlsx
@@ -457,10 +457,10 @@
     <row r="5" spans="1:8" ht="30" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
-        <v>1</v>
+        <v>30960001</v>
       </c>
       <c r="C5" s="2">
-        <v>1001</v>
+        <v>41000001</v>
       </c>
       <c r="D5" s="2">
         <v>5</v>
@@ -481,10 +481,10 @@
     <row r="6" spans="1:8" ht="30" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
-        <v>2</v>
+        <v>30960002</v>
       </c>
       <c r="C6" s="2">
-        <v>1001</v>
+        <v>41000001</v>
       </c>
       <c r="D6" s="2">
         <v>8</v>
@@ -505,10 +505,10 @@
     <row r="7" spans="1:8" ht="30" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
-        <v>3</v>
+        <v>30960003</v>
       </c>
       <c r="C7" s="2">
-        <v>1001</v>
+        <v>41000001</v>
       </c>
       <c r="D7" s="2">
         <v>8</v>
@@ -529,10 +529,10 @@
     <row r="8" spans="1:8" ht="30" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
-        <v>4</v>
+        <v>30960004</v>
       </c>
       <c r="C8" s="2">
-        <v>1001</v>
+        <v>41000001</v>
       </c>
       <c r="D8" s="2">
         <v>12</v>
@@ -553,10 +553,10 @@
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
-        <v>5</v>
+        <v>30960005</v>
       </c>
       <c r="C9" s="2">
-        <v>1001</v>
+        <v>41000001</v>
       </c>
       <c r="D9" s="2">
         <v>10</v>
@@ -577,10 +577,10 @@
     <row r="10" spans="1:8" ht="30" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2">
-        <v>6</v>
+        <v>30960006</v>
       </c>
       <c r="C10" s="2">
-        <v>1001</v>
+        <v>41000001</v>
       </c>
       <c r="D10" s="2">
         <v>15</v>
